--- a/src/assets/templates/weekly-invoice-margin-template.xlsx
+++ b/src/assets/templates/weekly-invoice-margin-template.xlsx
@@ -89,10 +89,10 @@
     <t>[profit_amount]</t>
   </si>
   <si>
-    <t xml:space="preserve">   [total_sum]</t>
-  </si>
-  <si>
     <t>[total_profit]</t>
+  </si>
+  <si>
+    <t>[total_sum=sum_without_vat+vat_sum+margin_amount]</t>
   </si>
 </sst>
 </file>
@@ -329,6 +329,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -347,59 +374,32 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -697,28 +697,28 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
       <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="24"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="8"/>
@@ -727,83 +727,83 @@
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="21" t="s">
+      <c r="C5" s="16"/>
+      <c r="D5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="16" t="s">
+      <c r="E5" s="16"/>
+      <c r="F5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="16" t="s">
+      <c r="G5" s="26"/>
+      <c r="H5" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="16" t="s">
+      <c r="I5" s="26"/>
+      <c r="J5" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="16" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="31"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="32" t="s">
+      <c r="M5" s="35"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="P5" s="33"/>
+      <c r="P5" s="20"/>
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="19" t="s">
+      <c r="C6" s="14"/>
+      <c r="D6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="34" t="s">
+      <c r="E6" s="14"/>
+      <c r="F6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="19" t="s">
+      <c r="G6" s="28"/>
+      <c r="H6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="19" t="s">
+      <c r="I6" s="14"/>
+      <c r="J6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="20"/>
-      <c r="L6" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="29"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="12" t="s">
+      <c r="K6" s="14"/>
+      <c r="L6" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="33"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="22"/>
     </row>
     <row r="7" spans="1:16" ht="15.75" thickBot="1">
       <c r="I7" s="9"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="26"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" s="15"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" s="24"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
@@ -817,13 +817,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="O6:P6"/>
     <mergeCell ref="O7:P7"/>
@@ -836,6 +829,13 @@
     <mergeCell ref="L5:N5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
